--- a/data/trans_orig/P6907S1-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6907S1-Clase-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>3749</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13730</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12087</t>
+          <t>12307</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7815</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22162</t>
+          <t>22139</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51353</t>
+          <t>51474</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61448</t>
+          <t>61334</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34563</t>
+          <t>34343</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44531</t>
+          <t>43893</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>89571</t>
+          <t>89594</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104051</t>
+          <t>103918</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,01%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14832</t>
+          <t>15210</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>9708</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21048</t>
+          <t>20858</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27523</t>
+          <t>27145</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39310</t>
+          <t>39388</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31629</t>
+          <t>31908</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40439</t>
+          <t>40465</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62922</t>
+          <t>63112</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>77615</t>
+          <t>78105</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>93,01%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18263</t>
+          <t>17373</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19375</t>
+          <t>19195</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81767</t>
+          <t>82657</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95273</t>
+          <t>96135</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11993</t>
+          <t>11974</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>96941</t>
+          <t>97121</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111309</t>
+          <t>111390</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>6702</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20787</t>
+          <t>21079</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13177</t>
+          <t>13559</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11947</t>
+          <t>11869</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28888</t>
+          <t>29029</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>180042</t>
+          <t>179750</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>194152</t>
+          <t>194127</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36769</t>
+          <t>36387</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46726</t>
+          <t>46388</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>221887</t>
+          <t>221746</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>238828</t>
+          <t>238906</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13418</t>
+          <t>13813</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11006</t>
+          <t>10441</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20257</t>
+          <t>20426</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50591</t>
+          <t>50196</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61345</t>
+          <t>61332</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54617</t>
+          <t>55182</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63689</t>
+          <t>63637</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>109375</t>
+          <t>109206</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>123665</t>
+          <t>123626</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2438,107 +2438,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>43508</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32292</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57892</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23625</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15931</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35361</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>63</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>67134</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>52127</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84594</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -2551,107 +2551,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>410</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>428797</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>414413</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>440013</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>192</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>196496</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>184760</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>204190</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>602</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>625293</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>607833</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>640300</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -2664,462 +2664,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472305</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472305</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472305</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>215</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220121</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220121</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220121</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>665</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>43508</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>31374</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>57283</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>12,13%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>23625</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>16145</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>34298</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>10,73%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>7,33%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>15,58%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>67134</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>52223</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>84638</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>9,7%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>12,22%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>428797</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>415022</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>440931</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>90,79%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>87,87%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>93,36%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>196496</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>185823</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>203976</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>89,27%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>84,42%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>92,67%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>625293</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>607789</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>640204</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>90,3%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>87,78%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>92,46%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>472305</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>472305</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>472305</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>220121</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>220121</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>220121</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>692427</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>692427</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>692427</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -3129,7 +2786,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3142,7 +2798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3173,7 +2829,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2012 (tasa de respuesta: 44,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,97 +3024,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1945</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1880</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5770</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>11,11%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>32,97%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1945</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6086</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>11,11%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5988</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>34,77%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1945</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>7554</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>4,83%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3137,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20857</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22737</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3152,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,7 +3172,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11418</t>
+          <t>11734</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3187,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,7 +3207,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32687</t>
+          <t>34253</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3566,7 +3222,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3716,7 +3372,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4464</t>
+          <t>4596</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3387,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3786,7 +3442,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6835</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3457,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>21,87%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3480,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16214</t>
+          <t>16082</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3839,7 +3495,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3894,7 +3550,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20018</t>
+          <t>20980</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3909,7 +3565,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4054,12 +3710,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>924</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8334</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +3725,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +3745,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +3760,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +3780,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>930</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>7918</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4167,12 +3823,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24063</t>
+          <t>25237</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31463</t>
+          <t>31473</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +3838,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +3858,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18401</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20331</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +3873,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +3893,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44805</t>
+          <t>44809</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51799</t>
+          <t>51797</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4397,12 +4053,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9067</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4068,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4088,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4103,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4123,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9236</t>
+          <t>10050</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4138,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4166,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44376</t>
+          <t>44248</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52412</t>
+          <t>52443</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4181,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4201,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33346</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35269</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4216,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4236,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>79476</t>
+          <t>78662</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>87675</t>
+          <t>87686</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4251,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -4740,97 +4396,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2090</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2086</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2174</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4509,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11233</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13323</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4524,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4544,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18796</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4559,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4579,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32030</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34204</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4594,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +4719,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5073,107 +4729,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7827</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15108</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>865</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10676</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5467</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18786</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -5186,107 +4842,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>130</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>134750</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>127469</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>138869</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>97312</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>92869</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>99296</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>221</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>232062</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>223952</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>237271</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -5299,462 +4955,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>138</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>142577</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>142577</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>142577</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100161</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100161</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100161</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>232</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>242738</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>242738</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>242738</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>7827</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>3828</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>13864</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>9,72%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>2849</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>901</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>7739</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>7,73%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>10676</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>5690</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>18377</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>7,57%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>134750</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>128713</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>138749</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>94,51%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>90,28%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>97,32%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>97312</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>92422</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>99260</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>97,16%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>92,27%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>232062</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>224361</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>237048</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>95,6%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>92,43%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>97,66%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>142577</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>142577</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>142577</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>100161</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>100161</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>100161</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>242738</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>242738</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>242738</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -5764,7 +5077,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5777,7 +5089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5808,7 +5120,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6008,7 +5320,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +5335,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +5355,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +5370,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6078,7 +5390,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6093,7 +5405,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -6116,7 +5428,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40766</t>
+          <t>42194</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6131,7 +5443,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,7 +5463,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39764</t>
+          <t>40993</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +5478,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,7 +5498,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86178</t>
+          <t>86150</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6201,7 +5513,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6351,7 +5663,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +5678,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,62 +5693,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1763</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1932</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5713</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1763</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5494</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -6459,7 +5771,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24680</t>
+          <t>24580</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6474,7 +5786,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,12 +5806,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27462</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29394</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +5821,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,7 +5841,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>54137</t>
+          <t>53918</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -6544,7 +5856,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6689,12 +6001,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10812</t>
+          <t>11066</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6016,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6036,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6051,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6071,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12139</t>
+          <t>11870</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6086,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6114,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56078</t>
+          <t>55824</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64871</t>
+          <t>64825</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6129,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6149,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9569</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6164,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6184,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64320</t>
+          <t>64589</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74363</t>
+          <t>74472</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6199,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -7037,7 +6349,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7052,7 +6364,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7072,7 +6384,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6926</t>
+          <t>6850</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7087,7 +6399,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +6414,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>933</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>10061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +6429,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -7145,7 +6457,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>130226</t>
+          <t>131158</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7160,7 +6472,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7180,7 +6492,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77151</t>
+          <t>77227</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7195,7 +6507,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7215,12 +6527,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>211245</t>
+          <t>210885</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>220007</t>
+          <t>220013</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +6542,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -7380,7 +6692,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7011</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7395,7 +6707,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7415,7 +6727,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7430,7 +6742,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +6757,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +6772,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -7488,7 +6800,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62084</t>
+          <t>61915</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -7503,7 +6815,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7523,7 +6835,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38902</t>
+          <t>39923</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7538,7 +6850,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7558,12 +6870,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>105812</t>
+          <t>106492</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>115395</t>
+          <t>115412</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +6885,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7010,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7708,107 +7020,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12203</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20359</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29009</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -7821,107 +7133,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>310</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>337798</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>329642</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>343846</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>202</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>210964</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>203460</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214384</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>512</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>548761</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>537290</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>555834</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -7934,462 +7246,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>322</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350001</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350001</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350001</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>207</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216298</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216298</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216298</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>529</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566299</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566299</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566299</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>12203</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>6822</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>21090</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>5334</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1873</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>11770</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>5,44%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>17538</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>10744</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>26956</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>337798</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>328911</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>343179</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>96,51%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>93,97%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>98,05%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>210964</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>204528</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>214425</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>97,53%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>94,56%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>548761</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>539343</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>555555</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>96,9%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>95,24%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>350001</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>350001</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>350001</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>216298</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>216298</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>216298</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>529</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>566299</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>566299</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>566299</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -8399,7 +7368,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8412,7 +7380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8443,7 +7411,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +7606,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>974</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8620</t>
+          <t>9048</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +7621,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +7641,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12499</t>
+          <t>12216</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +7656,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +7676,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6165</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17257</t>
+          <t>17564</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +7691,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +7719,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37196</t>
+          <t>36768</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44742</t>
+          <t>44842</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +7734,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +7754,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46791</t>
+          <t>47074</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55591</t>
+          <t>55538</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +7769,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +7789,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>87849</t>
+          <t>87542</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98941</t>
+          <t>98634</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +7804,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,84%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +7949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1693</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10917</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +7964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +7984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13968</t>
+          <t>13668</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +7999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +8019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22210</t>
+          <t>20718</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +8034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +8062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39862</t>
+          <t>40256</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48952</t>
+          <t>49086</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +8077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +8097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28190</t>
+          <t>28490</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39372</t>
+          <t>39746</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +8112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +8132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>70727</t>
+          <t>72219</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>87034</t>
+          <t>87082</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +8147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +8292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8010</t>
+          <t>7954</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23826</t>
+          <t>24189</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +8307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +8327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>471</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +8342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +8362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>9187</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26087</t>
+          <t>25707</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +8377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,67%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +8405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34697</t>
+          <t>34334</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50513</t>
+          <t>50569</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +8420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +8440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>12366</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17343</t>
+          <t>17368</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +8455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +8475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50275</t>
+          <t>50655</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67251</t>
+          <t>67175</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +8490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,97%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +8635,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5722</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17980</t>
+          <t>17653</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +8650,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +8670,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14707</t>
+          <t>14512</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +8685,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +8705,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11475</t>
+          <t>11746</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27916</t>
+          <t>28813</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +8720,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +8748,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>115238</t>
+          <t>115565</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>127496</t>
+          <t>128120</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +8763,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +8783,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>91051</t>
+          <t>91246</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>101913</t>
+          <t>101774</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +8798,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +8818,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>211060</t>
+          <t>210163</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>227501</t>
+          <t>227230</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +8833,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,08%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +8978,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>9755</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +8993,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +9013,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>8248</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10065,7 +9033,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +9048,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15281</t>
+          <t>14640</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +9063,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +9091,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41894</t>
+          <t>41415</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50124</t>
+          <t>49877</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +9106,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +9126,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>118933</t>
+          <t>118999</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>126125</t>
+          <t>126126</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,7 +9141,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -10193,12 +9161,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>163135</t>
+          <t>163776</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>175151</t>
+          <t>175366</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +9176,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -10333,7 +9301,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10343,107 +9311,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36776</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26360</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51777</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27447</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18770</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>40044</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>74</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>64223</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46700</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>80229</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -10456,107 +9424,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>303</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>302729</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>287728</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>313145</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>432</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>324845</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>312248</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>333522</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>735</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>627574</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>611568</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>645097</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -10569,462 +9537,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>338</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339505</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339505</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339505</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>471</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352292</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352292</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352292</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>809</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>691797</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>691797</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>691797</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>36776</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>26759</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>51294</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>10,83%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>7,88%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>15,11%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>27447</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>17678</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>38585</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>7,79%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>10,95%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>64223</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>48028</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>82907</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>9,28%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>11,98%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>302729</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>288211</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>312746</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>89,17%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>84,89%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>92,12%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>324845</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>313707</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>334614</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>92,21%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>89,05%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>94,98%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>735</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>627574</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>608890</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>643769</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>90,72%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>88,02%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>93,06%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>339505</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>339505</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>339505</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>352292</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>352292</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>352292</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>809</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>691797</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>691797</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>691797</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -11034,7 +9659,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
